--- a/Vikash Sinha-Docs.xlsx
+++ b/Vikash Sinha-Docs.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T460\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_Prac021026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19155" windowHeight="6780"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19160" windowHeight="6780" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction of DevOps" sheetId="1" r:id="rId1"/>
-    <sheet name="VSCode_Details" sheetId="9" r:id="rId2"/>
-    <sheet name="Devops|Devsecops|Cloud-Tools" sheetId="8" r:id="rId3"/>
-    <sheet name="Git &amp; Github" sheetId="2" r:id="rId4"/>
-    <sheet name="Terraform(IaC)" sheetId="3" r:id="rId5"/>
-    <sheet name="Ansible(Configur-Management)" sheetId="4" r:id="rId6"/>
-    <sheet name="Docker(Containerisation)" sheetId="5" r:id="rId7"/>
-    <sheet name="Kubernetes(Container-Orchestrat" sheetId="6" r:id="rId8"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId9"/>
+    <sheet name="VS-GitTortoise-GitKraken-ST" sheetId="10" r:id="rId2"/>
+    <sheet name="VSCode_Details" sheetId="9" r:id="rId3"/>
+    <sheet name="Devops|Devsecops|Cloud-Tools" sheetId="8" r:id="rId4"/>
+    <sheet name="Git &amp; Github" sheetId="2" r:id="rId5"/>
+    <sheet name="Terraform(IaC)" sheetId="3" r:id="rId6"/>
+    <sheet name="Ansible(Configur-Management)" sheetId="4" r:id="rId7"/>
+    <sheet name="Docker(Containerisation)" sheetId="5" r:id="rId8"/>
+    <sheet name="Kubernetes(Container-Orchestrat" sheetId="6" r:id="rId9"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="408">
   <si>
     <t>DevOps LifeCyle Stages and Trending Tools</t>
   </si>
@@ -1273,12 +1274,153 @@
   <si>
     <t>Key Differences</t>
   </si>
+  <si>
+    <t>GitKraken</t>
+  </si>
+  <si>
+    <t>Standalone Desktop Git GUI</t>
+  </si>
+  <si>
+    <t>Code Editor / IDE with Git</t>
+  </si>
+  <si>
+    <t>Dedicated Git GUI</t>
+  </si>
+  <si>
+    <t>Windows Shell Extension</t>
+  </si>
+  <si>
+    <t>Interface Style</t>
+  </si>
+  <si>
+    <t>Sleek, modern dark/light UI with interactive drag-and-drop graphs</t>
+  </si>
+  <si>
+    <t>Editor-centric with sidebar Git pane</t>
+  </si>
+  <si>
+    <t>Traditional tabbed desktop app</t>
+  </si>
+  <si>
+    <t>Windows right-click context menu</t>
+  </si>
+  <si>
+    <t>Cross-Platform</t>
+  </si>
+  <si>
+    <t>Licensing</t>
+  </si>
+  <si>
+    <t>Freemium (Paid for private repos/enterprise)</t>
+  </si>
+  <si>
+    <t>Free &amp; Open Source</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Standout Features</t>
+  </si>
+  <si>
+    <t>Drag-and-drop rebasing/merging, built-in terminal, workspace views, pull request management</t>
+  </si>
+  <si>
+    <t>Write code and manage basic Git in one window</t>
+  </si>
+  <si>
+    <t>Free enterprise choice, deep Bitbucket integration</t>
+  </si>
+  <si>
+    <t>Direct File Explorer integration without opening an app</t>
+  </si>
+  <si>
+    <t>What Makes GitKraken Unique?</t>
+  </si>
+  <si>
+    <t>1. Interactive Visual Commit Graph</t>
+  </si>
+  <si>
+    <t>Unlike VS Code’s basic SCM pane or Sourcetree’s traditional graph, GitKraken’s commit graph is fully interactive. You can drag and drop one branch onto another to trigger a merge or interactive rebase directly from the graph.</t>
+  </si>
+  <si>
+    <t>2. Built-in PR and Issue Tracking</t>
+  </si>
+  <si>
+    <t>GitKraken integrates directly with platforms like GitHub, GitLab, Bitbucket, and Azure DevOps. You can create, edit, review, and merge Pull Requests directly inside the client, as well as link issue trackers like Jira, Trello, or GitHub Issues.</t>
+  </si>
+  <si>
+    <t>3. Workspace &amp; Team Collaboration Features</t>
+  </si>
+  <si>
+    <t>It offers team-centric features like "Workspaces," which let teams organize multiple repositories, monitor pull requests across projects, and see who is working on what branches in real time to avoid merge conflicts before they happen.</t>
+  </si>
+  <si>
+    <t>4. Integrated Terminal</t>
+  </si>
+  <si>
+    <t>It includes a built-in terminal tab that stays synchronized with the GUI. If you change branches in the terminal, the GUI automatically updates to reflect the change, giving you the flexibility of both CLI and GUI simultaneously.</t>
+  </si>
+  <si>
+    <t>5. Pricing Difference</t>
+  </si>
+  <si>
+    <t>Unlike VS Code, Sourcetree, and TortoiseGit (which are completely free), GitKraken uses a freemium model. While free for public repositories, you need a paid subscription (GitKraken Pro/Teams) to use it with private repositories or enterprise features.</t>
+  </si>
+  <si>
+    <t>Which Should You Use?</t>
+  </si>
+  <si>
+    <r>
+      <t>Use VS Code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for 90% of daily development (writing code, making simple commits, pulling/pushing).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Use GitKraken</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if you want the most visually intuitive, modern GUI for managing complex git trees, handling multi-repo workspaces, and reviewing Pull Requests visually without leaving a dedicated Git tool.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Use Sourcetree</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if you need a free dedicated GUI alternative to GitKraken for private repositories.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1339,6 +1481,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1404,7 +1559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1462,9 +1617,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1488,6 +1640,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1818,33 +1988,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" customWidth="1"/>
+    <col min="2" max="2" width="25.26953125" customWidth="1"/>
+    <col min="3" max="3" width="41.7265625" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" customWidth="1"/>
-    <col min="7" max="7" width="36.140625" customWidth="1"/>
-    <col min="8" max="11" width="20.42578125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="34.7265625" customWidth="1"/>
+    <col min="7" max="7" width="36.1796875" customWidth="1"/>
+    <col min="8" max="11" width="20.453125" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="2" spans="1:11" ht="17.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="H2" s="27" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+    </row>
+    <row r="2" spans="1:11" ht="17.5">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="H2" s="26" t="s">
         <v>372</v>
       </c>
     </row>
@@ -1868,7 +2038,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="75">
+    <row r="4" spans="1:11" ht="72.5">
       <c r="A4" s="7">
         <v>1</v>
       </c>
@@ -1887,20 +2057,20 @@
       <c r="G4" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="27" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30">
+    <row r="5" spans="1:11" ht="29">
       <c r="A5" s="7">
         <v>2</v>
       </c>
@@ -1914,20 +2084,20 @@
         <v>337</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="28" t="s">
         <v>350</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="28" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="90">
+    <row r="6" spans="1:11" ht="87">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -1943,20 +2113,20 @@
       <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="27" t="s">
         <v>352</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="28" t="s">
         <v>353</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="28" t="s">
         <v>354</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="28" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="57">
+    <row r="7" spans="1:11" ht="42">
       <c r="A7" s="7"/>
       <c r="B7" s="5" t="s">
         <v>149</v>
@@ -1968,20 +2138,20 @@
         <v>340</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="28" t="s">
         <v>357</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="28" t="s">
         <v>358</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="28" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="42.75">
+    <row r="8" spans="1:11" ht="28">
       <c r="A8" s="7">
         <v>4</v>
       </c>
@@ -1995,20 +2165,20 @@
         <v>11</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="27" t="s">
         <v>360</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="28" t="s">
         <v>361</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J8" s="28" t="s">
         <v>362</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="28" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="105">
+    <row r="9" spans="1:11" ht="101.5">
       <c r="A9" s="7">
         <v>5</v>
       </c>
@@ -2024,20 +2194,20 @@
       <c r="E9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="28" t="s">
         <v>365</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="28" t="s">
         <v>366</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="28" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="90">
+    <row r="10" spans="1:11" ht="87">
       <c r="A10" s="7">
         <v>6</v>
       </c>
@@ -2053,20 +2223,20 @@
       <c r="E10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="27" t="s">
         <v>368</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="28" t="s">
         <v>369</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="28" t="s">
         <v>370</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="28" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="75">
+    <row r="11" spans="1:11" ht="72.5">
       <c r="A11" s="7">
         <v>7</v>
       </c>
@@ -2083,7 +2253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="30">
+    <row r="12" spans="1:11" ht="29">
       <c r="A12" s="7">
         <v>8</v>
       </c>
@@ -2099,25 +2269,25 @@
       <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="23" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="D15" s="25"/>
-    </row>
-    <row r="16" spans="1:11" ht="18">
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:11" ht="17.5">
       <c r="A16" s="10" t="s">
         <v>32</v>
       </c>
@@ -2127,7 +2297,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="30">
+    <row r="18" spans="1:4" ht="29">
       <c r="B18" s="11" t="s">
         <v>34</v>
       </c>
@@ -2138,7 +2308,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30">
+    <row r="19" spans="1:4" ht="29">
       <c r="B19" s="5" t="s">
         <v>37</v>
       </c>
@@ -2149,7 +2319,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30">
+    <row r="20" spans="1:4" ht="29">
       <c r="B20" s="5" t="s">
         <v>38</v>
       </c>
@@ -2160,7 +2330,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="45">
+    <row r="21" spans="1:4" ht="43.5">
       <c r="B21" s="5" t="s">
         <v>39</v>
       </c>
@@ -2171,7 +2341,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="45">
+    <row r="22" spans="1:4" ht="43.5">
       <c r="B22" s="5" t="s">
         <v>40</v>
       </c>
@@ -2189,7 +2359,7 @@
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
     </row>
-    <row r="25" spans="1:4" ht="75">
+    <row r="25" spans="1:4" ht="72.5">
       <c r="B25" s="15" t="s">
         <v>50</v>
       </c>
@@ -2197,7 +2367,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="60">
+    <row r="26" spans="1:4" ht="58">
       <c r="B26" s="5" t="s">
         <v>53</v>
       </c>
@@ -2205,7 +2375,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="60">
+    <row r="27" spans="1:4" ht="58">
       <c r="B27" s="5" t="s">
         <v>55</v>
       </c>
@@ -2223,1573 +2393,230 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E92"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
-    <col min="5" max="5" width="52.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
+    <col min="4" max="4" width="23.36328125" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5">
-      <c r="A2" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28">
+      <c r="A2" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="18">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="18">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="18">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="18">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="18">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="18">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="27.75">
-      <c r="A9" s="18">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>86</v>
-      </c>
+      <c r="B2" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42">
+      <c r="A3" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="28">
+      <c r="A4" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="42">
+      <c r="A5" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="70">
+      <c r="A6" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="17.5">
+      <c r="A8" s="10" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="32"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="18">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>90</v>
+      <c r="A10" s="33" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="18">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>93</v>
+      <c r="A11" s="34" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="18">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>97</v>
+      <c r="A12" s="33" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="18">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>100</v>
+      <c r="A13" s="34" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="18">
-        <v>12</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>104</v>
+      <c r="A14" s="33" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="18">
-        <v>13</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>107</v>
+      <c r="A15" s="34" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="18">
-        <v>14</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="18">
-        <v>15</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="18">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="18">
-        <v>18</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="18">
-        <v>19</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="18">
-        <v>20</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="18">
-        <v>21</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="18">
-        <v>22</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="30">
-      <c r="A25" s="18">
-        <v>23</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="18">
-        <v>24</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="18">
-        <v>25</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="18">
-        <v>26</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="18">
-        <v>27</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="30">
-      <c r="A30" s="18">
-        <v>28</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="18">
-        <v>29</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="18">
-        <v>30</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="18">
-        <v>31</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="18">
-        <v>32</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="18">
-        <v>33</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="18">
-        <v>34</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="18">
-        <v>35</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="18">
-        <v>36</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="18">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="30">
-      <c r="A40" s="18">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="18">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="18">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="18">
-        <v>41</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="18">
-        <v>42</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="18">
-        <v>43</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="18">
-        <v>44</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="18">
-        <v>45</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="18">
-        <v>46</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="18">
-        <v>47</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="18">
-        <v>48</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="18">
-        <v>49</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="18">
-        <v>50</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="18">
-        <v>51</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="18">
-        <v>52</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="18">
-        <v>53</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="18">
-        <v>54</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="18">
-        <v>55</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="18">
-        <v>56</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="18">
-        <v>57</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="18">
-        <v>58</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="18">
-        <v>59</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="18">
-        <v>60</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="18">
-        <v>61</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="18">
-        <v>62</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="18">
-        <v>63</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="18">
-        <v>64</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="18">
-        <v>65</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="18">
-        <v>66</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="18">
-        <v>67</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="18">
-        <v>68</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="18">
-        <v>69</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="18">
-        <v>70</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>278</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="18">
-        <v>71</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C73" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="18">
-        <v>72</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="18">
-        <v>73</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="18">
-        <v>74</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="18">
-        <v>75</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="18">
-        <v>76</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="18">
-        <v>77</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C79" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="18">
-        <v>78</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="18">
-        <v>79</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="C81" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="18">
-        <v>80</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="18">
-        <v>81</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C83" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="18">
-        <v>82</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C84" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="18">
-        <v>83</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C85" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="18">
-        <v>84</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="18">
-        <v>85</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C87" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="18">
-        <v>86</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C88" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="18">
-        <v>87</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="18">
-        <v>88</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C90" s="16" t="s">
-        <v>329</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="18">
-        <v>89</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="18">
-        <v>90</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E92" s="17" t="s">
-        <v>334</v>
-      </c>
+      <c r="A16" s="33" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="34" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="33" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="34" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="17.5">
+      <c r="A21" s="10" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="14" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="14" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="32"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="32"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="32"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="34"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="32"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="32"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="32"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3797,19 +2624,1584 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A2:E92"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="5" max="5" width="52.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5">
+      <c r="A2" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="18">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="18">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="18">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="18">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="18">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="18">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="27">
+      <c r="A9" s="18">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="18">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="18">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="18">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="18">
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="18">
+        <v>12</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="18">
+        <v>13</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="18">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="18">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="18">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="18">
+        <v>18</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="18">
+        <v>19</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="18">
+        <v>20</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="18">
+        <v>21</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="18">
+        <v>22</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="18">
+        <v>23</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="18">
+        <v>24</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="18">
+        <v>25</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="18">
+        <v>26</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="18">
+        <v>27</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="18">
+        <v>28</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="18">
+        <v>29</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="18">
+        <v>30</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="18">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="18">
+        <v>32</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="18">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="18">
+        <v>34</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="18">
+        <v>35</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="18">
+        <v>36</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="18">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="18">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="18">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="18">
+        <v>40</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="18">
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="18">
+        <v>42</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="18">
+        <v>43</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="18">
+        <v>44</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="18">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="18">
+        <v>46</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="18">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="18">
+        <v>48</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="18">
+        <v>49</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="18">
+        <v>50</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="18">
+        <v>51</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="18">
+        <v>52</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="18">
+        <v>53</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="18">
+        <v>54</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="18">
+        <v>55</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="18">
+        <v>56</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="18">
+        <v>57</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="18">
+        <v>58</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="18">
+        <v>59</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="18">
+        <v>60</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="18">
+        <v>61</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E63" s="17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="18">
+        <v>62</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="18">
+        <v>63</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="18">
+        <v>64</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="18">
+        <v>65</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="18">
+        <v>66</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="18">
+        <v>67</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="18">
+        <v>68</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="18">
+        <v>69</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="18">
+        <v>70</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="18">
+        <v>71</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="18">
+        <v>72</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="18">
+        <v>73</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C75" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="18">
+        <v>74</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="18">
+        <v>75</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C77" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="18">
+        <v>76</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="18">
+        <v>77</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C79" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="18">
+        <v>78</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="18">
+        <v>79</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="18">
+        <v>80</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="18">
+        <v>81</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="18">
+        <v>82</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="18">
+        <v>83</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="18">
+        <v>84</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C86" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="18">
+        <v>85</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="18">
+        <v>86</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="18">
+        <v>87</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="18">
+        <v>88</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="18">
+        <v>89</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="18">
+        <v>90</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E92" s="17" t="s">
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3818,7 +4210,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3827,7 +4219,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3836,7 +4228,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3845,7 +4237,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
